--- a/data/dividends_info_20260311.xlsx
+++ b/data/dividends_info_20260311.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.65000152587891</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>1.355275855411678</v>
+        <v>1.361867663851262</v>
       </c>
       <c r="J2" t="n">
         <v>348</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>22.20000076293945</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8783783481914642</v>
+        <v>0.8609271668175563</v>
       </c>
       <c r="J3" t="n">
         <v>103</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21.8700008392334</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="I4" t="n">
-        <v>3.886602502891329</v>
+        <v>3.926097066867768</v>
       </c>
       <c r="J4" t="n">
         <v>103</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.458000183105469</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I5" t="n">
-        <v>2.807370623405867</v>
+        <v>2.832812457787805</v>
       </c>
       <c r="J5" t="n">
         <v>103</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.77000045776367</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="I6" t="n">
-        <v>2.692664695208534</v>
+        <v>2.730696827919346</v>
       </c>
       <c r="J6" t="n">
         <v>68</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>33.95999908447266</v>
+        <v>33.18999862670898</v>
       </c>
       <c r="I7" t="n">
-        <v>5.889281666425159</v>
+        <v>6.025911668434178</v>
       </c>
       <c r="J7" t="n">
         <v>68</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4.070000171661377</v>
+        <v>3.930000066757202</v>
       </c>
       <c r="I8" t="n">
-        <v>2.457002353372873</v>
+        <v>2.544529218863702</v>
       </c>
       <c r="J8" t="n">
         <v>68</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>73.73999786376953</v>
+        <v>72.09999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>1.410360767736041</v>
+        <v>1.442441084618453</v>
       </c>
       <c r="J9" t="n">
         <v>68</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>51.65000152587891</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="I10" t="n">
-        <v>4.259438402722417</v>
+        <v>4.280155514961109</v>
       </c>
       <c r="J10" t="n">
         <v>68</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.820000052452087</v>
+        <v>1.825000047683716</v>
       </c>
       <c r="I11" t="n">
-        <v>2.197802134461918</v>
+        <v>2.191780764650821</v>
       </c>
       <c r="J11" t="n">
         <v>68</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19.55500030517578</v>
+        <v>19.41500091552734</v>
       </c>
       <c r="I12" t="n">
-        <v>4.03988743375731</v>
+        <v>4.069018608019686</v>
       </c>
       <c r="J12" t="n">
         <v>68</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.36299991607666</v>
+        <v>5.321000099182129</v>
       </c>
       <c r="I13" t="n">
-        <v>3.542793268193743</v>
+        <v>3.570757309874965</v>
       </c>
       <c r="J13" t="n">
         <v>68</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10.36999988555908</v>
+        <v>10.25</v>
       </c>
       <c r="I14" t="n">
-        <v>4.165863112511591</v>
+        <v>4.214634146341464</v>
       </c>
       <c r="J14" t="n">
         <v>68</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24.34000015258789</v>
+        <v>24.57999992370605</v>
       </c>
       <c r="I15" t="n">
-        <v>1.807723899924537</v>
+        <v>1.790073235824725</v>
       </c>
       <c r="J15" t="n">
         <v>68</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>55.29999923706055</v>
+        <v>53.7400016784668</v>
       </c>
       <c r="I16" t="n">
-        <v>2.531645604547781</v>
+        <v>2.605135757859436</v>
       </c>
       <c r="J16" t="n">
         <v>68</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.944000005722046</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I17" t="n">
-        <v>10.19021737149834</v>
+        <v>9.933774897176066</v>
       </c>
       <c r="J17" t="n">
         <v>68</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>30.54999923706055</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="I18" t="n">
-        <v>3.436988629205048</v>
+        <v>3.425774920288073</v>
       </c>
       <c r="J18" t="n">
         <v>68</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>23.19000053405762</v>
+        <v>23.31999969482422</v>
       </c>
       <c r="I19" t="n">
-        <v>2.587322062019014</v>
+        <v>2.57289883298398</v>
       </c>
       <c r="J19" t="n">
         <v>68</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8.600000381469727</v>
+        <v>8.560000419616699</v>
       </c>
       <c r="I20" t="n">
-        <v>5.93604624832303</v>
+        <v>5.963784754380411</v>
       </c>
       <c r="J20" t="n">
         <v>54</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>18.5</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I21" t="n">
-        <v>4.054054054054054</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J21" t="n">
         <v>54</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.934999942779541</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="I22" t="n">
-        <v>3.811944146917711</v>
+        <v>3.797468308588</v>
       </c>
       <c r="J22" t="n">
         <v>54</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>11.96000003814697</v>
+        <v>11.5600004196167</v>
       </c>
       <c r="I23" t="n">
-        <v>1.648570228855522</v>
+        <v>1.705614124939086</v>
       </c>
       <c r="J23" t="n">
         <v>54</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25.85000038146973</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>4.255319086140217</v>
+        <v>4.347826218068307</v>
       </c>
       <c r="J24" t="n">
         <v>54</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>10.25</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>3.707317073170731</v>
+        <v>3.743842505237692</v>
       </c>
       <c r="J25" t="n">
         <v>54</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6.695000171661377</v>
+        <v>6.605000019073486</v>
       </c>
       <c r="I27" t="n">
-        <v>7.468259703956423</v>
+        <v>7.570022688207914</v>
       </c>
       <c r="J27" t="n">
         <v>40</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>11.71500015258789</v>
+        <v>11.76500034332275</v>
       </c>
       <c r="I28" t="n">
-        <v>4.609474971971826</v>
+        <v>4.589885118928008</v>
       </c>
       <c r="J28" t="n">
         <v>40</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.407999992370605</v>
+        <v>6.328000068664551</v>
       </c>
       <c r="I29" t="n">
-        <v>1.560549315216299</v>
+        <v>1.580278111803242</v>
       </c>
       <c r="J29" t="n">
         <v>40</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>300.5</v>
+        <v>294.6000061035156</v>
       </c>
       <c r="I30" t="n">
-        <v>1.202995008319468</v>
+        <v>1.227087550951975</v>
       </c>
       <c r="J30" t="n">
         <v>40</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>26</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I31" t="n">
-        <v>5.230769230769231</v>
+        <v>5.074627010135566</v>
       </c>
       <c r="J31" t="n">
         <v>40</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>13.84000015258789</v>
+        <v>13.8100004196167</v>
       </c>
       <c r="I32" t="n">
-        <v>4.226878566114849</v>
+        <v>4.236060696776118</v>
       </c>
       <c r="J32" t="n">
         <v>40</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>16.15999984741211</v>
+        <v>16.5049991607666</v>
       </c>
       <c r="I33" t="n">
-        <v>3.898514888296174</v>
+        <v>3.817025337980924</v>
       </c>
       <c r="J33" t="n">
         <v>40</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>101.8000030517578</v>
+        <v>101.1999969482422</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8840864175047385</v>
+        <v>0.8893280900594264</v>
       </c>
       <c r="J34" t="n">
         <v>40</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>68.80999755859375</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="I35" t="n">
-        <v>2.500799391156333</v>
+        <v>2.545562187636385</v>
       </c>
       <c r="J35" t="n">
         <v>40</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>24.60000038146973</v>
+        <v>24.29999923706055</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5691056822318461</v>
+        <v>0.5761317053314243</v>
       </c>
       <c r="J36" t="n">
         <v>33</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.529999971389771</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I37" t="n">
-        <v>3.92156870078234</v>
+        <v>4.05405400180747</v>
       </c>
       <c r="J37" t="n">
         <v>33</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>20.8700008392334</v>
+        <v>21.28499984741211</v>
       </c>
       <c r="I38" t="n">
-        <v>1.245807328915998</v>
+        <v>1.221517509344082</v>
       </c>
       <c r="J38" t="n">
         <v>12</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>29.21999931335449</v>
+        <v>29.14500045776367</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3080082207902964</v>
+        <v>0.3088008186187066</v>
       </c>
       <c r="J39" t="n">
         <v>12</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>51.65000152587891</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="I40" t="n">
-        <v>1.258470437167987</v>
+        <v>1.2645914021476</v>
       </c>
       <c r="J40" t="n">
         <v>-16</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.490000009536743</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I41" t="n">
-        <v>4.026845611810072</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J41" t="n">
         <v>-30</v>
@@ -2379,7 +2379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C374"/>
+  <dimension ref="A1:C364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2436,7 +2436,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2742,7 +2742,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2752,14 +2752,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2820,14 +2820,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2878,7 +2878,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2888,14 +2888,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2990,14 +2990,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3024,14 +3024,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3092,14 +3092,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3160,14 +3160,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3194,14 +3194,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3252,29 +3252,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3286,12 +3286,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3303,7 +3303,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3330,14 +3330,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3364,19 +3364,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3388,12 +3388,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3405,46 +3405,46 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3456,12 +3456,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3473,29 +3473,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3507,12 +3507,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3524,12 +3524,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3592,7 +3592,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3602,14 +3602,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3619,14 +3619,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3653,14 +3653,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3694,12 +3694,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3711,12 +3711,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3728,12 +3728,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3745,12 +3745,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3762,12 +3762,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3779,46 +3779,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3830,12 +3830,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3847,12 +3847,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3864,63 +3864,63 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3932,46 +3932,46 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3983,12 +3983,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4000,12 +4000,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4017,24 +4017,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4044,70 +4044,70 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4119,12 +4119,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4153,12 +4153,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4170,29 +4170,29 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4221,7 +4221,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4265,14 +4265,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4289,7 +4289,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4299,14 +4299,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4323,7 +4323,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4350,14 +4350,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4374,12 +4374,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4408,12 +4408,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4425,12 +4425,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4442,12 +4442,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4459,46 +4459,46 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4510,12 +4510,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4527,29 +4527,29 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4561,12 +4561,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4578,12 +4578,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4595,29 +4595,29 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4629,12 +4629,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4646,12 +4646,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4680,12 +4680,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4765,7 +4765,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4782,7 +4782,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4799,7 +4799,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4901,7 +4901,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4928,19 +4928,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4952,12 +4952,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4969,12 +4969,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4986,29 +4986,29 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5020,12 +5020,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5037,29 +5037,29 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5071,29 +5071,29 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5132,14 +5132,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5190,7 +5190,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5207,7 +5207,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5241,29 +5241,29 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5275,80 +5275,80 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5360,12 +5360,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5377,29 +5377,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5428,7 +5428,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5462,7 +5462,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5479,7 +5479,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5513,7 +5513,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5547,7 +5547,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5564,7 +5564,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5591,19 +5591,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5632,12 +5632,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5649,29 +5649,29 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5683,12 +5683,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5700,12 +5700,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5717,46 +5717,46 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5768,7 +5768,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5853,7 +5853,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5880,14 +5880,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5921,7 +5921,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5955,7 +5955,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5972,7 +5972,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5989,7 +5989,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6023,7 +6023,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6033,14 +6033,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6050,14 +6050,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6084,19 +6084,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6108,29 +6108,29 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6142,12 +6142,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6159,12 +6159,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6176,12 +6176,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6210,12 +6210,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6227,12 +6227,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6244,12 +6244,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6312,7 +6312,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6356,14 +6356,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6380,7 +6380,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6397,7 +6397,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6414,7 +6414,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6431,7 +6431,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6465,7 +6465,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6482,7 +6482,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6499,7 +6499,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6516,7 +6516,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6526,14 +6526,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6550,7 +6550,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6567,7 +6567,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6601,7 +6601,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6618,7 +6618,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6635,7 +6635,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6645,14 +6645,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6703,12 +6703,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6720,12 +6720,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6737,29 +6737,29 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6771,12 +6771,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6788,12 +6788,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6805,12 +6805,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6822,12 +6822,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6839,12 +6839,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6856,12 +6856,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6873,7 +6873,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6924,7 +6924,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6941,7 +6941,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6975,7 +6975,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6992,7 +6992,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7009,7 +7009,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7026,7 +7026,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7094,7 +7094,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7104,14 +7104,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7128,7 +7128,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7145,7 +7145,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7155,14 +7155,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7172,14 +7172,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7196,7 +7196,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7213,7 +7213,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7230,7 +7230,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7264,7 +7264,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7281,7 +7281,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7315,7 +7315,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7332,7 +7332,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7383,7 +7383,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7400,7 +7400,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7417,7 +7417,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7451,7 +7451,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7468,7 +7468,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7485,7 +7485,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7502,7 +7502,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7512,14 +7512,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7536,7 +7536,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7553,7 +7553,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7570,7 +7570,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7587,7 +7587,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7604,7 +7604,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7621,12 +7621,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7638,12 +7638,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7655,12 +7655,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7672,29 +7672,29 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7706,12 +7706,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7723,12 +7723,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7740,12 +7740,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7757,34 +7757,34 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7818,14 +7818,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7842,7 +7842,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7886,14 +7886,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7910,7 +7910,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7927,7 +7927,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7961,7 +7961,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7978,7 +7978,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8029,7 +8029,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8056,14 +8056,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8080,7 +8080,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8090,14 +8090,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8114,7 +8114,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8131,7 +8131,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8148,7 +8148,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8158,14 +8158,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8182,7 +8182,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8199,7 +8199,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8216,7 +8216,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8226,14 +8226,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8267,12 +8267,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8284,46 +8284,46 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8335,46 +8335,46 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8386,80 +8386,80 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8471,46 +8471,46 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8522,221 +8522,51 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Masi Agricola S.p.A.</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8751,188 +8581,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001472171</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.820000052452087</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.197802134461918</v>
-      </c>
-      <c r="I2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005331019</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22.20000076293945</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8783783481914642</v>
-      </c>
-      <c r="I3" t="n">
-        <v>103</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0003549422</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>30.54999923706055</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3.436988629205048</v>
-      </c>
-      <c r="I4" t="n">
-        <v>68</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8943,146 +8594,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Masi Agricola S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>